--- a/docs/OxyPC_UAT_TestPlan.xlsx
+++ b/docs/OxyPC_UAT_TestPlan.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B71C1C"/>
     </font>
   </fonts>
   <fills count="11">
@@ -127,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -169,13 +173,19 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,6 +198,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -602,7 +615,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -614,7 +627,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>41</t>
         </is>
       </c>
     </row>
@@ -626,7 +639,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -638,7 +651,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -650,7 +663,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -747,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -925,14 +938,14 @@
           <t>HTTP 302 — page renders without error</t>
         </is>
       </c>
-      <c r="G3" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="G3" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I3" s="15" t="inlineStr"/>
@@ -996,7 +1009,7 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr"/>
@@ -1011,7 +1024,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr"/>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
@@ -1054,7 +1071,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr"/>
@@ -1071,7 +1088,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>Dashboard is at / (root) — no /dashboard prefix</t>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
         </is>
       </c>
     </row>
@@ -1109,14 +1126,14 @@
           <t>HTTP 302 — page renders without error</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr"/>
@@ -1178,7 +1195,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr"/>
@@ -1195,7 +1212,7 @@
       </c>
       <c r="M7" s="13" t="inlineStr">
         <is>
-          <t>Lots list is at /lots (not /stock/lots)</t>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1257,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr"/>
@@ -1257,7 +1274,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>New lot form is at /lots/new</t>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1319,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr"/>
@@ -1317,7 +1334,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr"/>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -1360,7 +1381,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr"/>
@@ -1375,7 +1396,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -1418,7 +1443,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr"/>
@@ -1433,7 +1458,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M11" s="13" t="inlineStr"/>
+      <c r="M11" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="60" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -1475,7 +1504,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr"/>
@@ -1490,7 +1519,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr"/>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1532,7 +1565,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr"/>
@@ -1547,7 +1580,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M13" s="13" t="inlineStr"/>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -1589,7 +1626,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr"/>
@@ -1604,7 +1641,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M14" s="13" t="inlineStr"/>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -1647,7 +1688,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr"/>
@@ -1662,7 +1703,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M15" s="13" t="inlineStr"/>
+      <c r="M15" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
@@ -1698,14 +1743,14 @@
           <t>HTTP 422 — page renders without error</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="G16" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>400</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr"/>
@@ -1767,7 +1812,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I17" s="15" t="inlineStr"/>
@@ -1782,12 +1827,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M17" s="13" t="inlineStr"/>
+      <c r="M17" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="60" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>P1-REP-02</t>
+          <t>P1-REP-04</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -1802,14 +1851,14 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Repair L2 page</t>
+          <t>Repair L3/L4 page</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
           <t>1. Log in as admin
-2. Navigate to http://192.168.4.8:8000/repair/l2
-3. Verify Level-2 repair queue page loads</t>
+2. Navigate to http://192.168.4.8:8000/repair/l3l4
+3. Verify the L3/L4 repair queue page loads</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -1824,7 +1873,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr"/>
@@ -1839,12 +1888,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M18" s="13" t="inlineStr"/>
+      <c r="M18" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="60" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>P1-REP-03</t>
+          <t>P1-QC-01</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -1854,72 +1907,15 @@
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>QC</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Repair L3 page</t>
+          <t>QC main page</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>1. Log in as admin
-2. Navigate to http://192.168.4.8:8000/repair/l3
-3. Verify Level-3 repair queue page loads</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>HTTP 200 — page renders without error</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I19" s="15" t="inlineStr"/>
-      <c r="J19" s="15" t="inlineStr"/>
-      <c r="K19" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="M19" s="13" t="inlineStr"/>
-    </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>P1-QC-01</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>QC main page</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>1. Log in as admin
 2. Navigate to http://192.168.4.8:8000/qc
@@ -1927,57 +1923,61 @@
 4. Verify grade/pass/fail buttons are visible</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>HTTP 200 — page renders without error</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I20" s="15" t="inlineStr"/>
-      <c r="J20" s="15" t="inlineStr"/>
-      <c r="K20" s="12" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I19" s="15" t="inlineStr"/>
+      <c r="J19" s="15" t="inlineStr"/>
+      <c r="K19" s="12" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L19" s="16" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="M20" s="13" t="inlineStr"/>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="M19" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>P1-STK-01</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Stock overview page</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>1. Log in as admin
 2. Navigate to http://192.168.4.8:8000/stock
@@ -1985,61 +1985,61 @@
 4. Verify device count by stage is displayed</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>HTTP 200 — page renders without error</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I21" s="15" t="inlineStr"/>
-      <c r="J21" s="15" t="inlineStr"/>
-      <c r="K21" s="12" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I20" s="15" t="inlineStr"/>
+      <c r="J20" s="15" t="inlineStr"/>
+      <c r="K20" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L21" s="12" t="inlineStr">
+      <c r="L20" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M21" s="13" t="inlineStr">
-        <is>
-          <t>/stock is the stock overview page (distinct from /lots which is lot management)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="M20" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>P1-TRF-01</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Transfers</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Transfers page</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>1. Log in as admin
 2. Navigate to http://192.168.4.8:8000/transfers
@@ -2047,57 +2047,61 @@
 4. Verify transfer history is shown</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>HTTP 200 — page renders without error</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I22" s="15" t="inlineStr"/>
-      <c r="J22" s="15" t="inlineStr"/>
-      <c r="K22" s="12" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I21" s="15" t="inlineStr"/>
+      <c r="J21" s="15" t="inlineStr"/>
+      <c r="K21" s="12" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="L22" s="12" t="inlineStr">
+      <c r="L21" s="12" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="M22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="M21" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>P1-SAL-01</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Sales list page</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>1. Log in as admin
 2. Navigate to http://192.168.4.8:8000/sales
@@ -2105,57 +2109,61 @@
 4. Verify columns: Order ID, Dealer, Date, Amount, Status</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>HTTP 200 — page renders without error</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I23" s="15" t="inlineStr"/>
-      <c r="J23" s="15" t="inlineStr"/>
-      <c r="K23" s="12" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I22" s="15" t="inlineStr"/>
+      <c r="J22" s="15" t="inlineStr"/>
+      <c r="K22" s="12" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
+      <c r="L22" s="16" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="M23" s="13" t="inlineStr"/>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="M22" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>P1-INV-01</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Invoices</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Invoice print page - route exists</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>1. Log in as admin
 2. Open an existing sale order from http://192.168.4.8:8000/sales
@@ -2163,34 +2171,34 @@
 4. Verify invoice PDF/print view renders with sale details, items, line totals, grand total</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>HTTP 302 — page renders without error</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="I24" s="15" t="inlineStr"/>
-      <c r="J24" s="15" t="inlineStr"/>
-      <c r="K24" s="12" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="H23" s="12" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr"/>
+      <c r="J23" s="15" t="inlineStr"/>
+      <c r="K23" s="12" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr">
+      <c r="L23" s="16" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="M24" s="13" t="inlineStr">
+      <c r="M23" s="13" t="inlineStr">
         <is>
           <t>Auto-test uses a dummy UUID so expects 307/404 redirect; manual test must use a real sale ID from /sales</t>
         </is>
@@ -2198,7 +2206,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"PASS,FAIL,BLOCKED,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2338,7 +2346,7 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr"/>
@@ -2353,7 +2361,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M2" s="13" t="inlineStr"/>
+      <c r="M2" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
@@ -2396,7 +2408,7 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I3" s="15" t="inlineStr"/>
@@ -2411,7 +2423,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr"/>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
@@ -2454,7 +2470,7 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr"/>
@@ -2469,7 +2485,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M4" s="13" t="inlineStr"/>
+      <c r="M4" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
@@ -2512,7 +2532,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr"/>
@@ -2527,7 +2547,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M5" s="13" t="inlineStr"/>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
@@ -2570,7 +2594,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr"/>
@@ -2585,7 +2609,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr"/>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -2628,7 +2656,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr"/>
@@ -2643,7 +2671,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M7" s="13" t="inlineStr"/>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -2686,7 +2718,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr"/>
@@ -2703,7 +2735,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>/reports/ has no landing index page; use /reports/lot-pl or /reports/receivables directly</t>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2781,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr"/>
@@ -2764,7 +2796,11 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr"/>
+      <c r="M9" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="60" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
@@ -2807,7 +2843,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr"/>
@@ -2822,7 +2858,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -2865,7 +2905,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr"/>
@@ -2882,7 +2922,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>Inventory location router prefix is /locations (not /inventory-location)</t>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3068,7 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr"/>
@@ -3045,7 +3085,7 @@
       </c>
       <c r="M2" s="13" t="inlineStr">
         <is>
-          <t>/crm (no trailing slash) returns 307 redirect to /crm/</t>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3130,7 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I3" s="15" t="inlineStr"/>
@@ -3105,7 +3145,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M3" s="13" t="inlineStr"/>
+      <c r="M3" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
@@ -3148,7 +3192,7 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr"/>
@@ -3165,7 +3209,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>/crm/activities has no index; use /crm/activities/followups</t>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3254,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr"/>
@@ -3225,7 +3269,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M5" s="13" t="inlineStr"/>
+      <c r="M5" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
@@ -3268,7 +3316,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr"/>
@@ -3283,7 +3331,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M6" s="13" t="inlineStr"/>
+      <c r="M6" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
@@ -3326,7 +3378,7 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr"/>
@@ -3341,7 +3393,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M7" s="13" t="inlineStr"/>
+      <c r="M7" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
@@ -3384,7 +3440,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I8" s="15" t="inlineStr"/>
@@ -3399,7 +3455,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M8" s="13" t="inlineStr"/>
+      <c r="M8" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
@@ -3435,14 +3495,14 @@
           <t>HTTP 200 — page renders without error</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="G9" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>404</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr"/>
@@ -3500,7 +3560,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr"/>
@@ -3515,7 +3575,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -3558,7 +3622,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I11" s="15" t="inlineStr"/>
@@ -3575,7 +3639,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>/admin has no index page; admin entry point is /admin/users</t>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3684,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr"/>
@@ -3635,7 +3699,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr"/>
+      <c r="M12" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="60" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -3678,7 +3746,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr"/>
@@ -3693,7 +3761,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M13" s="13" t="inlineStr"/>
+      <c r="M13" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="60" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -3736,7 +3808,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I14" s="15" t="inlineStr"/>
@@ -3751,7 +3823,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="M14" s="13" t="inlineStr"/>
+      <c r="M14" s="13" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3890,14 +3966,14 @@
           <t>HTTP 403 — page renders without error</t>
         </is>
       </c>
-      <c r="G2" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="G2" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>403</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I2" s="15" t="inlineStr"/>
@@ -4014,14 +4090,14 @@
           <t>HTTP 429 — page renders without error</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>307</t>
         </is>
       </c>
       <c r="I4" s="15" t="inlineStr"/>
@@ -4038,7 +4114,7 @@
       </c>
       <c r="M4" s="13" t="inlineStr">
         <is>
-          <t>Hit 429 after burst: True; last status: 429</t>
+          <t>Hit 429 after burst: False; last status: 307</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4071,150 +4147,335 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B1" s="17" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>Gap / Issue</t>
         </is>
       </c>
-      <c r="C1" s="17" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>Business Impact</t>
         </is>
       </c>
-      <c r="D1" s="17" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>Effort</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>CSRF protection NOT enforcing 403</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Any authenticated user can forge mutation requests — data integrity at risk</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>Dev Team</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>SEC-01: Expected 403 got 307</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>No HTTPS — app runs on plain HTTP</t>
         </is>
       </c>
-      <c r="C2" s="19" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>All data including passwords transmitted in plaintext on network</t>
         </is>
       </c>
-      <c r="D2" s="19" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E2" s="19" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="F2" s="19" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>DevOps</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>App is configured to listen on HTTP only (config.ini host/port). For LAN internal use this is moderate risk; unacceptable for internet-facing deployment.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Backup runbook exists but no automated script confirmed</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Manual backup only — relies on operator discipline</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>DevOps</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>docs/backup-runbook.md present. Verify cron job / scheduled task is actually running.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Admin password is still default (oxypc@admin123)</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Low risk for LAN-only; high risk if ever internet-facing</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>WARN</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>Credentials: admin / oxypc@admin123 still in use. Change before any non-internal deployment. Not a go-live blocker for pure-LAN deployment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Phase 1 route failed: POST /auth/login</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Core workflow page broken — users blocked</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Dev Team</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Expected 302, got 307</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Phase 1 route failed: POST /auth/logout</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Core workflow page broken — users blocked</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>Dev Team</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Expected 302, got 307</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Phase 1 route failed: GET /iqc/api/users</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Core workflow page broken — users blocked</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>Dev Team</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>Expected 422, got 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Phase 1 route failed: GET /invoices/print/00000000-0000-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Core workflow page broken — users blocked</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Dev Team</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Expected 302, got 307</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4303,2467 +4564,2538 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>P1-AUTH-01</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>Phase 1</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>Login page renders</t>
         </is>
       </c>
-      <c r="E2" s="21" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>GET</t>
         </is>
       </c>
-      <c r="F2" s="21" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>/auth/login</t>
         </is>
       </c>
-      <c r="G2" s="21" t="n">
+      <c r="G2" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="H2" s="21" t="inlineStr">
+      <c r="H2" s="23" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J2" s="21" t="n">
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J2" s="23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K2" s="23" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>P1-AUTH-02</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>Login with valid credentials</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>/auth/login</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="n">
+        <v>302</v>
+      </c>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I3" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K3" s="25" t="inlineStr">
+        <is>
+          <t>Expected 302 redirect with Set-Cookie access_token</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>P1-AUTH-03</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Login with wrong password shows error</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>/auth/login</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>P1-AUTH-04</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>Dashboard accessible after login</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H5" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>P1-AUTH-05</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>Logout redirects to login</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>/auth/logout</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>302</v>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I6" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>Logout is a POST endpoint, not GET — use the Logout button in UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>P1-LOTS-01</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Lots &amp; GRN</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Lots list page</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>/lots</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>P1-LOTS-02</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Lots &amp; GRN</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>New Lot form</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>/lots/new</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>P1-LOTS-03</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Lots &amp; GRN</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>GRN list page</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>/grn</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H9" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K9" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>P1-DEV-01</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Devices list - all stages</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>/devices</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>P1-DEV-02</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>Devices filtered by stage=iqc</t>
+        </is>
+      </c>
+      <c r="E11" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
+        <is>
+          <t>/devices?stage=iqc</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H11" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K11" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>P1-DEV-03</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Devices filtered by stage=stock_in</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>/devices?stage=stock_in</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>P1-DEV-04</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>Devices filtered by stage=l1</t>
+        </is>
+      </c>
+      <c r="E13" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>/devices?stage=l1</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K13" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>P1-DEV-05</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Devices</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Devices filtered by stage=ready_to_sale</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>/devices?stage=ready_to_sale</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K14" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>P1-IQC-01</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>IQC</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>IQC main page</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>/iqc</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H15" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K15" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>P1-IQC-02</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>IQC</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>IQC API users endpoint</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>/iqc/api/users</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>422</v>
+      </c>
+      <c r="H16" s="23" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K16" s="23" t="inlineStr">
+        <is>
+          <t>Machine API — 422 expected without API-key header; /iqc/api/devices path does not exist</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>P1-REP-01</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>Repair</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>Repair L1 page</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>/repair/l1</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K17" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>P1-REP-04</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Repair</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Repair L3/L4 page</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>/repair/l3l4</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>P1-QC-01</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>QC main page</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>/qc</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>P1-STK-01</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>Stock overview page</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>/stock</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J20" s="23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K20" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>P1-TRF-01</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C21" s="25" t="inlineStr">
+        <is>
+          <t>Transfers</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>Transfers page</t>
+        </is>
+      </c>
+      <c r="E21" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
+        <is>
+          <t>/transfers</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H21" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K21" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>P1-SAL-01</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Sales list page</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>/sales</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>P1-INV-01</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>Phase 1</t>
+        </is>
+      </c>
+      <c r="C23" s="25" t="inlineStr">
+        <is>
+          <t>Invoices</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr">
+        <is>
+          <t>Invoice print page - route exists</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>/invoices/print/00000000-0000-0000-0000-000000000001</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="n">
+        <v>302</v>
+      </c>
+      <c r="H23" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I23" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K23" s="25" t="inlineStr">
+        <is>
+          <t>Auto-test uses a dummy UUID so expects 307/404 redirect; manual test must use a real sale ID from /sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>P2-DLR-01</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>Dealers list page</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>/dealers</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K24" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t>P2-DLR-02</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>Dealer ageing report</t>
+        </is>
+      </c>
+      <c r="E25" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
+        <is>
+          <t>/dealers/ageing</t>
+        </is>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H25" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K25" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>P2-DLR-03</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>Dealers</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>Dealer overdue report</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>/dealers/overdue</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J26" s="23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K26" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>P2-ACC-01</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>Accounts index page</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
+        <is>
+          <t>/accounts</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H27" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K27" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>P2-ACC-02</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>Customer receipts page</t>
+        </is>
+      </c>
+      <c r="E28" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>/accounts/customer-receipts</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J28" s="23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K28" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>P2-ACC-03</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>Supplier payments page</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
+        <is>
+          <t>/accounts/supplier-payments</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H29" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K29" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>P2-RPT-01</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>Reports - Lot P&amp;L page</t>
+        </is>
+      </c>
+      <c r="E30" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>/reports/lot-pl</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>P2-RPT-02</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>Receivables report</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>/reports/receivables</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H31" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n">
         <v>6.9</v>
       </c>
-      <c r="K2" s="21" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="23" t="inlineStr">
-        <is>
-          <t>P1-AUTH-02</t>
-        </is>
-      </c>
-      <c r="B3" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="K31" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>P2-RPT-03</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="inlineStr">
+        <is>
+          <t>Reports</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>Receivables CSV export</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
+          <t>/reports/receivables?export=csv</t>
+        </is>
+      </c>
+      <c r="G32" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>P2-LOC-01</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Phase 2</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>Inventory Location</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>Inventory location master page</t>
+        </is>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="inlineStr">
+        <is>
+          <t>/locations/master</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H33" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K33" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>P3-CRM-01</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>CRM dashboard</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
+          <t>/crm/</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J34" s="23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K34" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>P3-CRM-02</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>CRM Contacts</t>
+        </is>
+      </c>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>/crm/contacts</t>
+        </is>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H35" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K35" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>P3-CRM-03</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>CRM Activities - Follow-ups</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
+          <t>/crm/activities/followups</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J36" s="23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K36" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>P3-CRM-04</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>CRM Sourcing</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
+        <is>
+          <t>/crm/sourcing</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K37" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>P3-CRM-05</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="inlineStr">
+        <is>
+          <t>CRM Sales pipeline</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
+          <t>/crm/sales</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J38" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K38" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>P3-CRM-06</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>CRM Quotes</t>
+        </is>
+      </c>
+      <c r="E39" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F39" s="25" t="inlineStr">
+        <is>
+          <t>/crm/quotes</t>
+        </is>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H39" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J39" s="25" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K39" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>P3-CRM-07</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>CRM Purchase Orders</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>/crm/purchase-orders</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H40" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J40" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>P3-WA-01</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>WhatsApp</t>
+        </is>
+      </c>
+      <c r="D41" s="25" t="inlineStr">
+        <is>
+          <t>WhatsApp page</t>
+        </is>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t>/whatsapp</t>
+        </is>
+      </c>
+      <c r="G41" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H41" s="25" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J41" s="25" t="n">
+        <v>9</v>
+      </c>
+      <c r="K41" s="25" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>P3-MKT-01</t>
+        </is>
+      </c>
+      <c r="B42" s="23" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C42" s="23" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Market page</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>/market</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H42" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J42" s="23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K42" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>P3-ADM-01</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>Admin users list</t>
+        </is>
+      </c>
+      <c r="E43" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t>/admin/users</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H43" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J43" s="25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K43" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
+        <is>
+          <t>P3-ADM-02</t>
+        </is>
+      </c>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>Admin audit log</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>/admin/audit-log</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H44" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J44" s="23" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K44" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>P3-SET-01</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>Settings page</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>/settings</t>
+        </is>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H45" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J45" s="25" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K45" s="25" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="inlineStr">
+        <is>
+          <t>P3-ATT-01</t>
+        </is>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Phase 3</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>Attendance</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>Attendance page</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>/attendance</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H46" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J46" s="23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K46" s="23" t="inlineStr">
+        <is>
+          <t>Got 307 redirect (trailing-slash redirect) — acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>SEC-01</t>
+        </is>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="inlineStr">
+        <is>
+          <t>CSRF</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>POST mutation without CSRF token returns 403</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="inlineStr">
+        <is>
+          <t>/dealers/00000000-0000-0000-0000-000000000000/credit-notes/00000000-0000-0000-0000-000000000001/apply</t>
+        </is>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>403</v>
+      </c>
+      <c r="H47" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I47" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J47" s="25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K47" s="25" t="inlineStr">
+        <is>
+          <t>Double-submit CSRF protection must return 403 when token is absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>SEC-02</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
         <is>
           <t>Auth</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
-        <is>
-          <t>Login with valid credentials</t>
-        </is>
-      </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>Unauthenticated /admin/users redirects to login</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>/admin/users</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>307</v>
+      </c>
+      <c r="H48" s="23" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J48" s="23" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K48" s="23" t="inlineStr">
+        <is>
+          <t>FastAPI returns 307 (not 302) for auth redirects — both are safe redirects to /auth/login</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>SEC-03</t>
+        </is>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>Rate Limiting</t>
+        </is>
+      </c>
+      <c r="D49" s="25" t="inlineStr">
+        <is>
+          <t>Login rate limit triggers 429</t>
+        </is>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
         <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F49" s="25" t="inlineStr">
         <is>
           <t>/auth/login</t>
         </is>
       </c>
-      <c r="G3" s="23" t="n">
-        <v>302</v>
-      </c>
-      <c r="H3" s="23" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="I3" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J3" s="23" t="n">
-        <v>229.8</v>
-      </c>
-      <c r="K3" s="23" t="inlineStr">
-        <is>
-          <t>Expected 302 redirect with Set-Cookie access_token</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>P1-AUTH-03</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>Auth</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>Login with wrong password shows error</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>/auth/login</t>
-        </is>
-      </c>
-      <c r="G4" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I4" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>225.6</v>
-      </c>
-      <c r="K4" s="21" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>P1-AUTH-04</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="inlineStr">
-        <is>
-          <t>Auth</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
-        <is>
-          <t>Dashboard accessible after login</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F5" s="23" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H5" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I5" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J5" s="23" t="n">
-        <v>433.1</v>
-      </c>
-      <c r="K5" s="23" t="inlineStr">
-        <is>
-          <t>Dashboard is at / (root) — no /dashboard prefix</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>P1-AUTH-05</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C6" s="21" t="inlineStr">
-        <is>
-          <t>Auth</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>Logout redirects to login</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>/auth/logout</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>302</v>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="I6" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K6" s="21" t="inlineStr">
-        <is>
-          <t>Logout is a POST endpoint, not GET — use the Logout button in UI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>P1-LOTS-01</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C7" s="23" t="inlineStr">
-        <is>
-          <t>Lots &amp; GRN</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>Lots list page</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
-        <is>
-          <t>/lots</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H7" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I7" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J7" s="23" t="n">
-        <v>181.9</v>
-      </c>
-      <c r="K7" s="23" t="inlineStr">
-        <is>
-          <t>Lots list is at /lots (not /stock/lots)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>P1-LOTS-02</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>Lots &amp; GRN</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>New Lot form</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>/lots/new</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I8" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="K8" s="21" t="inlineStr">
-        <is>
-          <t>New lot form is at /lots/new</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>P1-LOTS-03</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>Lots &amp; GRN</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>GRN list page</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>/grn</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H9" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="n">
-        <v>54</v>
-      </c>
-      <c r="K9" s="23" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="21" t="inlineStr">
-        <is>
-          <t>P1-DEV-01</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>Devices</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>Devices list - all stages</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>/devices</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="K10" s="21" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>P1-DEV-02</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>Devices</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>Devices filtered by stage=iqc</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F11" s="23" t="inlineStr">
-        <is>
-          <t>/devices?stage=iqc</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H11" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="K11" s="23" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>P1-DEV-03</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>Devices</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>Devices filtered by stage=stock_in</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>/devices?stage=stock_in</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="K12" s="21" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>P1-DEV-04</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
-        <is>
-          <t>Devices</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Devices filtered by stage=l1</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F13" s="23" t="inlineStr">
-        <is>
-          <t>/devices?stage=l1</t>
-        </is>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H13" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="n">
-        <v>93.7</v>
-      </c>
-      <c r="K13" s="23" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>P1-DEV-05</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>Devices</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>Devices filtered by stage=ready_to_sale</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>/devices?stage=ready_to_sale</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="K14" s="21" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>P1-IQC-01</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>IQC</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>IQC main page</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F15" s="23" t="inlineStr">
-        <is>
-          <t>/iqc</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H15" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J15" s="23" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="K15" s="23" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="inlineStr">
-        <is>
-          <t>P1-IQC-02</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>IQC</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>IQC API users endpoint</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>/iqc/api/users</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>422</v>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K16" s="21" t="inlineStr">
-        <is>
-          <t>Machine API — 422 expected without API-key header; /iqc/api/devices path does not exist</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t>P1-REP-01</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>Repair</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>Repair L1 page</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F17" s="23" t="inlineStr">
-        <is>
-          <t>/repair/l1</t>
-        </is>
-      </c>
-      <c r="G17" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H17" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J17" s="23" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="K17" s="23" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="inlineStr">
-        <is>
-          <t>P1-REP-02</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>Repair</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>Repair L2 page</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>/repair/l2</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J18" s="21" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="K18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>P1-REP-03</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>Repair</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>Repair L3 page</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F19" s="23" t="inlineStr">
-        <is>
-          <t>/repair/l3</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H19" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J19" s="23" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="K19" s="23" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>P1-QC-01</t>
-        </is>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>QC main page</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>/qc</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J20" s="21" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="K20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>P1-STK-01</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C21" s="23" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="D21" s="23" t="inlineStr">
-        <is>
-          <t>Stock overview page</t>
-        </is>
-      </c>
-      <c r="E21" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F21" s="23" t="inlineStr">
-        <is>
-          <t>/stock</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H21" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J21" s="23" t="n">
-        <v>188.3</v>
-      </c>
-      <c r="K21" s="23" t="inlineStr">
-        <is>
-          <t>/stock is the stock overview page (distinct from /lots which is lot management)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>P1-TRF-01</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>Transfers</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>Transfers page</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>/transfers</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="n">
-        <v>71</v>
-      </c>
-      <c r="K22" s="21" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>P1-SAL-01</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C23" s="23" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
-        <is>
-          <t>Sales list page</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
-        <is>
-          <t>/sales</t>
-        </is>
-      </c>
-      <c r="G23" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H23" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J23" s="23" t="n">
-        <v>131.4</v>
-      </c>
-      <c r="K23" s="23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
-          <t>P1-INV-01</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>Phase 1</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>Invoices</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>Invoice print page - route exists</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>/invoices/print/00000000-0000-0000-0000-000000000001</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="n">
-        <v>302</v>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>Auto-test uses a dummy UUID so expects 307/404 redirect; manual test must use a real sale ID from /sales</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>P2-DLR-01</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C25" s="23" t="inlineStr">
-        <is>
-          <t>Dealers</t>
-        </is>
-      </c>
-      <c r="D25" s="23" t="inlineStr">
-        <is>
-          <t>Dealers list page</t>
-        </is>
-      </c>
-      <c r="E25" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F25" s="23" t="inlineStr">
-        <is>
-          <t>/dealers</t>
-        </is>
-      </c>
-      <c r="G25" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H25" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J25" s="23" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="K25" s="23" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>P2-DLR-02</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>Dealers</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>Dealer ageing report</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>/dealers/ageing</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I26" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="K26" s="21" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>P2-DLR-03</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C27" s="23" t="inlineStr">
-        <is>
-          <t>Dealers</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>Dealer overdue report</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F27" s="23" t="inlineStr">
-        <is>
-          <t>/dealers/overdue</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H27" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J27" s="23" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="K27" s="23" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>P2-ACC-01</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>Accounts</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>Accounts index page</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>/accounts</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J28" s="21" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="K28" s="21" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>P2-ACC-02</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>Accounts</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>Customer receipts page</t>
-        </is>
-      </c>
-      <c r="E29" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F29" s="23" t="inlineStr">
-        <is>
-          <t>/accounts/customer-receipts</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H29" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I29" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J29" s="23" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="K29" s="23" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
-          <t>P2-ACC-03</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C30" s="21" t="inlineStr">
-        <is>
-          <t>Accounts</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>Supplier payments page</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
-        <is>
-          <t>/accounts/supplier-payments</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I30" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J30" s="21" t="n">
-        <v>159</v>
-      </c>
-      <c r="K30" s="21" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>P2-RPT-01</t>
-        </is>
-      </c>
-      <c r="B31" s="23" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C31" s="23" t="inlineStr">
-        <is>
-          <t>Reports</t>
-        </is>
-      </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>Reports - Lot P&amp;L page</t>
-        </is>
-      </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>/reports/lot-pl</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H31" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I31" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J31" s="23" t="n">
-        <v>71</v>
-      </c>
-      <c r="K31" s="23" t="inlineStr">
-        <is>
-          <t>/reports/ has no landing index page; use /reports/lot-pl or /reports/receivables directly</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="21" t="inlineStr">
-        <is>
-          <t>P2-RPT-02</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C32" s="21" t="inlineStr">
-        <is>
-          <t>Reports</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>Receivables report</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>/reports/receivables</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I32" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J32" s="21" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="K32" s="21" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>P2-RPT-03</t>
-        </is>
-      </c>
-      <c r="B33" s="23" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C33" s="23" t="inlineStr">
-        <is>
-          <t>Reports</t>
-        </is>
-      </c>
-      <c r="D33" s="23" t="inlineStr">
-        <is>
-          <t>Receivables CSV export</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F33" s="23" t="inlineStr">
-        <is>
-          <t>/reports/receivables?export=csv</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H33" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I33" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J33" s="23" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K33" s="23" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="21" t="inlineStr">
-        <is>
-          <t>P2-LOC-01</t>
-        </is>
-      </c>
-      <c r="B34" s="21" t="inlineStr">
-        <is>
-          <t>Phase 2</t>
-        </is>
-      </c>
-      <c r="C34" s="21" t="inlineStr">
-        <is>
-          <t>Inventory Location</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>Inventory location master page</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
-        <is>
-          <t>/locations/master</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I34" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="n">
-        <v>67</v>
-      </c>
-      <c r="K34" s="21" t="inlineStr">
-        <is>
-          <t>Inventory location router prefix is /locations (not /inventory-location)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>P3-CRM-01</t>
-        </is>
-      </c>
-      <c r="B35" s="23" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C35" s="23" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="D35" s="23" t="inlineStr">
-        <is>
-          <t>CRM dashboard</t>
-        </is>
-      </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>/crm/</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H35" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I35" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J35" s="23" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="K35" s="23" t="inlineStr">
-        <is>
-          <t>/crm (no trailing slash) returns 307 redirect to /crm/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>P3-CRM-02</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C36" s="21" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>CRM Contacts</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>/crm/contacts</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I36" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J36" s="21" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="K36" s="21" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>P3-CRM-03</t>
-        </is>
-      </c>
-      <c r="B37" s="23" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C37" s="23" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="D37" s="23" t="inlineStr">
-        <is>
-          <t>CRM Activities - Follow-ups</t>
-        </is>
-      </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>/crm/activities/followups</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H37" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I37" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J37" s="23" t="n">
-        <v>65</v>
-      </c>
-      <c r="K37" s="23" t="inlineStr">
-        <is>
-          <t>/crm/activities has no index; use /crm/activities/followups</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>P3-CRM-04</t>
-        </is>
-      </c>
-      <c r="B38" s="21" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C38" s="21" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>CRM Sourcing</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>/crm/sourcing</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I38" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J38" s="21" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="K38" s="21" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>P3-CRM-05</t>
-        </is>
-      </c>
-      <c r="B39" s="23" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C39" s="23" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="D39" s="23" t="inlineStr">
-        <is>
-          <t>CRM Sales pipeline</t>
-        </is>
-      </c>
-      <c r="E39" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F39" s="23" t="inlineStr">
-        <is>
-          <t>/crm/sales</t>
-        </is>
-      </c>
-      <c r="G39" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H39" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I39" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J39" s="23" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="K39" s="23" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>P3-CRM-06</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="D40" s="21" t="inlineStr">
-        <is>
-          <t>CRM Quotes</t>
-        </is>
-      </c>
-      <c r="E40" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F40" s="21" t="inlineStr">
-        <is>
-          <t>/crm/quotes</t>
-        </is>
-      </c>
-      <c r="G40" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H40" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I40" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J40" s="21" t="n">
-        <v>55</v>
-      </c>
-      <c r="K40" s="21" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>P3-CRM-07</t>
-        </is>
-      </c>
-      <c r="B41" s="23" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C41" s="23" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="D41" s="23" t="inlineStr">
-        <is>
-          <t>CRM Purchase Orders</t>
-        </is>
-      </c>
-      <c r="E41" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F41" s="23" t="inlineStr">
-        <is>
-          <t>/crm/purchase-orders</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H41" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I41" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J41" s="23" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="K41" s="23" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="21" t="inlineStr">
-        <is>
-          <t>P3-WA-01</t>
-        </is>
-      </c>
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C42" s="21" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="D42" s="21" t="inlineStr">
-        <is>
-          <t>WhatsApp page</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F42" s="21" t="inlineStr">
-        <is>
-          <t>/whatsapp</t>
-        </is>
-      </c>
-      <c r="G42" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H42" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I42" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J42" s="21" t="n">
-        <v>2897.6</v>
-      </c>
-      <c r="K42" s="21" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>P3-MKT-01</t>
-        </is>
-      </c>
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C43" s="23" t="inlineStr">
-        <is>
-          <t>Market</t>
-        </is>
-      </c>
-      <c r="D43" s="23" t="inlineStr">
-        <is>
-          <t>Market page</t>
-        </is>
-      </c>
-      <c r="E43" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F43" s="23" t="inlineStr">
-        <is>
-          <t>/market</t>
-        </is>
-      </c>
-      <c r="G43" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H43" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I43" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J43" s="23" t="n">
-        <v>145.8</v>
-      </c>
-      <c r="K43" s="23" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="21" t="inlineStr">
-        <is>
-          <t>P3-ADM-01</t>
-        </is>
-      </c>
-      <c r="B44" s="21" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C44" s="21" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D44" s="21" t="inlineStr">
-        <is>
-          <t>Admin users list</t>
-        </is>
-      </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F44" s="21" t="inlineStr">
-        <is>
-          <t>/admin/users</t>
-        </is>
-      </c>
-      <c r="G44" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H44" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I44" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J44" s="21" t="n">
-        <v>94.3</v>
-      </c>
-      <c r="K44" s="21" t="inlineStr">
-        <is>
-          <t>/admin has no index page; admin entry point is /admin/users</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t>P3-ADM-02</t>
-        </is>
-      </c>
-      <c r="B45" s="23" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C45" s="23" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
-        <is>
-          <t>Admin audit log</t>
-        </is>
-      </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>/admin/audit-log</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H45" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I45" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J45" s="23" t="n">
-        <v>76</v>
-      </c>
-      <c r="K45" s="23" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="21" t="inlineStr">
-        <is>
-          <t>P3-SET-01</t>
-        </is>
-      </c>
-      <c r="B46" s="21" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C46" s="21" t="inlineStr">
-        <is>
-          <t>Settings</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>Settings page</t>
-        </is>
-      </c>
-      <c r="E46" s="21" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F46" s="21" t="inlineStr">
-        <is>
-          <t>/settings</t>
-        </is>
-      </c>
-      <c r="G46" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H46" s="21" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I46" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J46" s="21" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="K46" s="21" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>P3-ATT-01</t>
-        </is>
-      </c>
-      <c r="B47" s="23" t="inlineStr">
-        <is>
-          <t>Phase 3</t>
-        </is>
-      </c>
-      <c r="C47" s="23" t="inlineStr">
-        <is>
-          <t>Attendance</t>
-        </is>
-      </c>
-      <c r="D47" s="23" t="inlineStr">
-        <is>
-          <t>Attendance page</t>
-        </is>
-      </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>/attendance</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="H47" s="23" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="I47" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J47" s="23" t="n">
-        <v>64.40000000000001</v>
-      </c>
-      <c r="K47" s="23" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="21" t="inlineStr">
-        <is>
-          <t>SEC-01</t>
-        </is>
-      </c>
-      <c r="B48" s="21" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C48" s="21" t="inlineStr">
-        <is>
-          <t>CSRF</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>POST mutation without CSRF token returns 403</t>
-        </is>
-      </c>
-      <c r="E48" s="21" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F48" s="21" t="inlineStr">
-        <is>
-          <t>/dealers/00000000-0000-0000-0000-000000000000/credit-notes/00000000-0000-0000-0000-000000000001/apply</t>
-        </is>
-      </c>
-      <c r="G48" s="21" t="n">
-        <v>403</v>
-      </c>
-      <c r="H48" s="21" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="I48" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J48" s="21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K48" s="21" t="inlineStr">
-        <is>
-          <t>Double-submit CSRF protection must return 403 when token is absent</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>SEC-02</t>
-        </is>
-      </c>
-      <c r="B49" s="23" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C49" s="23" t="inlineStr">
-        <is>
-          <t>Auth</t>
-        </is>
-      </c>
-      <c r="D49" s="23" t="inlineStr">
-        <is>
-          <t>Unauthenticated /admin/users redirects to login</t>
-        </is>
-      </c>
-      <c r="E49" s="23" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="F49" s="23" t="inlineStr">
-        <is>
-          <t>/admin/users</t>
-        </is>
-      </c>
-      <c r="G49" s="23" t="n">
-        <v>307</v>
-      </c>
-      <c r="H49" s="23" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="I49" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J49" s="23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K49" s="23" t="inlineStr">
-        <is>
-          <t>FastAPI returns 307 (not 302) for auth redirects — both are safe redirects to /auth/login</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>SEC-03</t>
-        </is>
-      </c>
-      <c r="B50" s="21" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C50" s="21" t="inlineStr">
-        <is>
-          <t>Rate Limiting</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>Login rate limit triggers 429</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t>/auth/login</t>
-        </is>
-      </c>
-      <c r="G50" s="21" t="n">
+      <c r="G49" s="25" t="n">
         <v>429</v>
       </c>
-      <c r="H50" s="21" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="I50" s="22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="J50" s="21" t="n">
-        <v>5993.6</v>
-      </c>
-      <c r="K50" s="21" t="inlineStr">
-        <is>
-          <t>Hit 429 after burst: True; last status: 429</t>
+      <c r="H49" s="25" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="I49" s="26" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J49" s="25" t="n">
+        <v>198.8</v>
+      </c>
+      <c r="K49" s="25" t="inlineStr">
+        <is>
+          <t>Hit 429 after burst: False; last status: 307</t>
         </is>
       </c>
     </row>
